--- a/src/test/resources/TestData4.xlsx
+++ b/src/test/resources/TestData4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KSIDC\AI_Beacon_KSIDC_CustomerPortal\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A40667-888F-48E2-912E-4236C8AB51D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{194E3406-0DBD-4E25-82C6-FDDE994D9E1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" firstSheet="24" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" firstSheet="26" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KSIDC_Registration" sheetId="11" r:id="rId1"/>
@@ -41,8 +41,9 @@
     <sheet name="KSIDC_MeansOfFinance" sheetId="37" r:id="rId26"/>
     <sheet name="KSIDC_CollateralSecurity" sheetId="40" r:id="rId27"/>
     <sheet name="KSIDC-BankProfile" sheetId="41" r:id="rId28"/>
-    <sheet name="KSIDC_SecurityLand" sheetId="38" r:id="rId29"/>
-    <sheet name="KSIDC_SecurityVehicle" sheetId="39" r:id="rId30"/>
+    <sheet name="KSIDC-SubmitApplication" sheetId="42" r:id="rId29"/>
+    <sheet name="KSIDC_SecurityLand" sheetId="38" r:id="rId30"/>
+    <sheet name="KSIDC_SecurityVehicle" sheetId="39" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="437">
   <si>
     <t>Yes</t>
   </si>
@@ -1362,6 +1363,9 @@
   </si>
   <si>
     <t>ReTypeAccountNumber</t>
+  </si>
+  <si>
+    <t>Submit Application</t>
   </si>
 </sst>
 </file>
@@ -3340,38 +3344,39 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6432D31-EA2A-4778-92B9-58B3DD2450E3}">
-  <dimension ref="A1:I2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9AD2168-7FAA-4474-806D-25DB94EA8533}">
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>416</v>
+        <v>436</v>
+      </c>
+      <c r="C2" s="7">
+        <v>9954327856</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3506,6 +3511,42 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6432D31-EA2A-4778-92B9-58B3DD2450E3}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF15593D-2C6B-43B1-A740-ED0A60E67282}">
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/test/resources/TestData4.xlsx
+++ b/src/test/resources/TestData4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20416"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git_KSIDC\KSIDC_CustomerPortal-master\AI_Beacon_KSIDC_CustomerPortal\src\test\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KSIDC\AI_Beacon_KSIDC_CustomerPortal\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{982CA779-91FE-410F-A4FA-8F661550DB9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9EF2EA-0E98-47AF-818C-75552A23036D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" firstSheet="16" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" firstSheet="17" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="KSIDC_Registration" sheetId="11" r:id="rId1"/>
@@ -31,7 +31,9 @@
     <sheet name="KSIDC_Security_Plant_Machinery" sheetId="27" r:id="rId16"/>
     <sheet name="KSIDC_Security_Land_Development" sheetId="28" r:id="rId17"/>
     <sheet name="KSIDC_Sec_Building_Civil_Work" sheetId="29" r:id="rId18"/>
-    <sheet name="KSIDC_Utilities" sheetId="30" r:id="rId19"/>
+    <sheet name="KSIDC_CollateralSecurity" sheetId="31" r:id="rId19"/>
+    <sheet name="KSIDC_SecurityVehicle" sheetId="32" r:id="rId20"/>
+    <sheet name="KSIDC_Utilities" sheetId="30" r:id="rId21"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="336">
   <si>
     <t>Yes</t>
   </si>
@@ -994,6 +996,63 @@
   </si>
   <si>
     <t>Security_Utilities_Module</t>
+  </si>
+  <si>
+    <t>TitleHolder</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>AadhaarNo</t>
+  </si>
+  <si>
+    <t>DocNo</t>
+  </si>
+  <si>
+    <t>SurveyNo</t>
+  </si>
+  <si>
+    <t>ResurveyNo</t>
+  </si>
+  <si>
+    <t>ExtentOfLandWet</t>
+  </si>
+  <si>
+    <t>ExtentOfLandDRY</t>
+  </si>
+  <si>
+    <t>Taluk</t>
+  </si>
+  <si>
+    <t>CostOfLandAsPerDocument</t>
+  </si>
+  <si>
+    <t>BuildingAge</t>
+  </si>
+  <si>
+    <t>BuildingArea</t>
+  </si>
+  <si>
+    <t>CostForTheBuilding</t>
+  </si>
+  <si>
+    <t>Collateral_Security</t>
+  </si>
+  <si>
+    <t>Silpa</t>
+  </si>
+  <si>
+    <t>Poovathingal</t>
+  </si>
+  <si>
+    <t>Thiroor</t>
+  </si>
+  <si>
+    <t>Kannur</t>
+  </si>
+  <si>
+    <t>SecurityVehicleModule</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1084,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1035,6 +1094,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1078,7 +1143,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1126,6 +1191,10 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="12" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2030,27 +2099,138 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9246B31E-A03A-4E46-B276-B46C856B05E8}">
-  <dimension ref="A1:B2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE08AF90-A458-4178-BC72-32E8D4D85DB3}">
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="16.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="13.5703125" customWidth="1"/>
+    <col min="12" max="13" width="15.5703125" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="15" max="15" width="25.140625" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" customWidth="1"/>
+    <col min="18" max="18" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="C1" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="P1" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="Q1" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
+        <v>330</v>
+      </c>
+      <c r="C2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E2" s="26">
+        <v>333333333333</v>
+      </c>
+      <c r="F2">
+        <v>765434556</v>
+      </c>
+      <c r="G2">
+        <v>7643545</v>
+      </c>
+      <c r="H2">
+        <v>26977</v>
+      </c>
+      <c r="I2">
+        <v>5455</v>
+      </c>
+      <c r="J2">
+        <v>765443</v>
+      </c>
+      <c r="K2">
+        <v>123456</v>
+      </c>
+      <c r="L2" t="s">
+        <v>333</v>
+      </c>
+      <c r="M2" t="s">
+        <v>334</v>
+      </c>
+      <c r="N2" t="s">
+        <v>334</v>
+      </c>
+      <c r="O2">
+        <v>65445534</v>
+      </c>
+      <c r="P2">
+        <v>5</v>
+      </c>
+      <c r="Q2">
+        <v>2500</v>
+      </c>
+      <c r="R2">
+        <v>4000000</v>
       </c>
     </row>
   </sheetData>
@@ -2147,6 +2327,68 @@
       </c>
       <c r="L2" s="8" t="s">
         <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3A24C26-CCA2-44BC-8C5F-6052FF980B15}">
+  <dimension ref="A1:I2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>335</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9246B31E-A03A-4E46-B276-B46C856B05E8}">
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>316</v>
       </c>
     </row>
   </sheetData>
